--- a/excel-files/QUEZON CITY/MASAMBONG ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/MASAMBONG ELEMENTARY SCHOOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="324" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CE96FB7-C39E-43E7-92DC-1D5AF24AAAC2}"/>
+  <xr:revisionPtr revIDLastSave="508" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1AD06F11-1D8E-4BBC-82CB-D05AD9D44895}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3525,7 +3525,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D2" s="1">
         <v>357</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
@@ -3553,7 +3553,7 @@
         <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D3" s="1">
         <v>357</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="21" customHeight="1">
@@ -3581,7 +3581,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="1">
         <v>357</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="25.5" customHeight="1">
@@ -3609,7 +3609,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D5" s="1">
         <v>357</v>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5">
@@ -3637,14 +3637,14 @@
         <v>13</v>
       </c>
       <c r="C6" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="5"/>
       <c r="G6" s="3">
         <f t="shared" si="0"/>
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="H6" s="4">
         <f t="shared" si="1"/>
@@ -3654,7 +3654,7 @@
     <row r="7" spans="1:8">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:8" ht="39.75" customHeight="1">
       <c r="A8" s="1">
@@ -3664,14 +3664,14 @@
         <v>8</v>
       </c>
       <c r="C8" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
@@ -3686,14 +3686,14 @@
         <v>10</v>
       </c>
       <c r="C9" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
@@ -3708,14 +3708,14 @@
         <v>11</v>
       </c>
       <c r="C10" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
@@ -3730,14 +3730,14 @@
         <v>12</v>
       </c>
       <c r="C11" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
@@ -3752,24 +3752,24 @@
         <v>13</v>
       </c>
       <c r="C12" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="15">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+      <c r="E13" s="8"/>
     </row>
     <row r="14" spans="1:8" ht="49.5" customHeight="1">
       <c r="A14" s="1">
@@ -4171,14 +4171,14 @@
         <v>15</v>
       </c>
       <c r="C31" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="5"/>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
@@ -4193,14 +4193,14 @@
         <v>17</v>
       </c>
       <c r="C32" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
@@ -4215,14 +4215,14 @@
         <v>13</v>
       </c>
       <c r="C33" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
@@ -4237,14 +4237,14 @@
         <v>11</v>
       </c>
       <c r="C34" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
@@ -4259,14 +4259,14 @@
         <v>18</v>
       </c>
       <c r="C35" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="5"/>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
@@ -4281,14 +4281,14 @@
         <v>14</v>
       </c>
       <c r="C36" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="5"/>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
@@ -4303,14 +4303,14 @@
         <v>19</v>
       </c>
       <c r="C37" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="5"/>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
@@ -4325,14 +4325,14 @@
         <v>20</v>
       </c>
       <c r="C38" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="5"/>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
@@ -4347,14 +4347,14 @@
         <v>21</v>
       </c>
       <c r="C39" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
@@ -4379,14 +4379,14 @@
         <v>15</v>
       </c>
       <c r="C41" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
@@ -4401,14 +4401,14 @@
         <v>17</v>
       </c>
       <c r="C42" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
@@ -4423,14 +4423,14 @@
         <v>13</v>
       </c>
       <c r="C43" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
@@ -4445,14 +4445,14 @@
         <v>11</v>
       </c>
       <c r="C44" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
@@ -4467,14 +4467,14 @@
         <v>18</v>
       </c>
       <c r="C45" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
@@ -4489,14 +4489,14 @@
         <v>14</v>
       </c>
       <c r="C46" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
@@ -4511,14 +4511,14 @@
         <v>19</v>
       </c>
       <c r="C47" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
@@ -4533,14 +4533,14 @@
         <v>20</v>
       </c>
       <c r="C48" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
@@ -4555,14 +4555,14 @@
         <v>21</v>
       </c>
       <c r="C49" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
@@ -4954,7 +4954,7 @@
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
+      <c r="E70" s="7"/>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
@@ -5144,7 +5144,7 @@
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
       <c r="D80" s="8"/>
-      <c r="E80" s="8"/>
+      <c r="E80" s="7"/>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
@@ -5334,7 +5334,7 @@
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
       <c r="D90" s="8"/>
-      <c r="E90" s="8"/>
+      <c r="E90" s="7"/>
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
@@ -5501,16 +5501,16 @@
     </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C1:E98" name="Textbooks"/>
-    <protectedRange sqref="F1:F98" name="SOURCE"/>
+    <protectedRange sqref="C91:E98 C90:D90 C81:E89 C80:D80 C71:E79 C70:D70 C1:E69" name="Textbooks"/>
+    <protectedRange sqref="F1:F98 E90 E80 E70" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E2:E6 E8:E12" xr:uid="{29D504B7-7F39-4695-8586-99B066550104}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5522,7 +5522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -5763,18 +5763,18 @@
         <v>8</v>
       </c>
       <c r="C5" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" ref="H5:H77" si="2">IF((D5-E5)&lt;0,0,(D5-E5))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" ref="I5:I77" si="3">IF((E5-D5)&lt;0,0,(E5-D5))</f>
@@ -5782,14 +5782,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" ref="N5" si="4">IF((J5-K5)&lt;0,0,(J5-K5))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" ref="O5" si="5">IF((K5-J5)&lt;0,0,(K5-J5))</f>
@@ -5797,14 +5797,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" ref="T5" si="6">IF((P5-Q5)&lt;0,0,(P5-Q5))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" ref="U5" si="7">IF((Q5-P5)&lt;0,0,(Q5-P5))</f>
@@ -5812,14 +5812,14 @@
       </c>
       <c r="V5" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" ref="Z5" si="8">IF((V5-W5)&lt;0,0,(V5-W5))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" ref="AA5" si="9">IF((W5-V5)&lt;0,0,(W5-V5))</f>
@@ -5834,18 +5834,18 @@
         <v>10</v>
       </c>
       <c r="C6" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="3"/>
@@ -5853,14 +5853,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" ref="N6:N69" si="10">IF((J6-K6)&lt;0,0,(J6-K6))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" ref="O6:O69" si="11">IF((K6-J6)&lt;0,0,(K6-J6))</f>
@@ -5868,14 +5868,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" ref="T6:T69" si="12">IF((P6-Q6)&lt;0,0,(P6-Q6))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" ref="U6:U69" si="13">IF((Q6-P6)&lt;0,0,(Q6-P6))</f>
@@ -5883,14 +5883,14 @@
       </c>
       <c r="V6" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" ref="Z6:Z69" si="14">IF((V6-W6)&lt;0,0,(V6-W6))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" ref="AA6:AA69" si="15">IF((W6-V6)&lt;0,0,(W6-V6))</f>
@@ -5905,18 +5905,18 @@
         <v>11</v>
       </c>
       <c r="C7" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="3"/>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="11"/>
@@ -5939,14 +5939,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="13"/>
@@ -5954,14 +5954,14 @@
       </c>
       <c r="V7" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="15"/>
@@ -5976,18 +5976,18 @@
         <v>12</v>
       </c>
       <c r="C8" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="3"/>
@@ -5995,14 +5995,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="11"/>
@@ -6010,14 +6010,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="13"/>
@@ -6025,14 +6025,14 @@
       </c>
       <c r="V8" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="15"/>
@@ -6047,18 +6047,18 @@
         <v>13</v>
       </c>
       <c r="C9" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="3"/>
@@ -6066,14 +6066,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="11"/>
@@ -6081,14 +6081,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="13"/>
@@ -6096,14 +6096,14 @@
       </c>
       <c r="V9" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="15"/>
@@ -6118,18 +6118,18 @@
         <v>15</v>
       </c>
       <c r="C10" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -6137,14 +6137,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="11"/>
@@ -6152,14 +6152,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="13"/>
@@ -6167,14 +6167,14 @@
       </c>
       <c r="V10" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="15"/>
@@ -6189,18 +6189,18 @@
         <v>17</v>
       </c>
       <c r="C11" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E11" s="5"/>
       <c r="F11" s="1"/>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
         <f>IF((D11-E11)&lt;0,0,(D11-E11))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I11" s="5">
         <f>IF((E11-D11)&lt;0,0,(E11-D11))</f>
@@ -6208,14 +6208,14 @@
       </c>
       <c r="J11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="1"/>
       <c r="M11" s="5"/>
       <c r="N11" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O11" s="5">
         <f t="shared" si="11"/>
@@ -6223,14 +6223,14 @@
       </c>
       <c r="P11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="1"/>
       <c r="S11" s="5"/>
       <c r="T11" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U11" s="5">
         <f t="shared" si="13"/>
@@ -6238,14 +6238,14 @@
       </c>
       <c r="V11" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W11" s="5"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="5"/>
       <c r="Z11" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA11" s="5">
         <f t="shared" si="15"/>
@@ -6260,18 +6260,18 @@
         <v>63</v>
       </c>
       <c r="C12" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f>IF((D12-E12)&lt;0,0,(D12-E12))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I12" s="5">
         <f>IF((E12-D12)&lt;0,0,(E12-D12))</f>
@@ -6279,14 +6279,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="10"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="11"/>
@@ -6294,14 +6294,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="12"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="13"/>
@@ -6309,14 +6309,14 @@
       </c>
       <c r="V12" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="14"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="15"/>
@@ -6344,18 +6344,18 @@
         <v>8</v>
       </c>
       <c r="C14" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="3"/>
@@ -6363,14 +6363,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="11"/>
@@ -6378,14 +6378,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="13"/>
@@ -6393,14 +6393,14 @@
       </c>
       <c r="V14" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="15"/>
@@ -6415,18 +6415,18 @@
         <v>10</v>
       </c>
       <c r="C15" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="3"/>
@@ -6434,14 +6434,14 @@
       </c>
       <c r="J15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="1"/>
       <c r="M15" s="5"/>
       <c r="N15" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="11"/>
@@ -6449,14 +6449,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="13"/>
@@ -6464,14 +6464,14 @@
       </c>
       <c r="V15" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="15"/>
@@ -6486,11 +6486,11 @@
         <v>11</v>
       </c>
       <c r="C16" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E16" s="5">
         <v>302</v>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="H16" s="5">
         <f t="shared" si="2"/>
-        <v>1946</v>
+        <v>1962</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="3"/>
@@ -6511,14 +6511,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="11"/>
@@ -6526,14 +6526,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="13"/>
@@ -6541,14 +6541,14 @@
       </c>
       <c r="V16" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="15"/>
@@ -6563,11 +6563,11 @@
         <v>12</v>
       </c>
       <c r="C17" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E17" s="5">
         <v>302</v>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="H17" s="5">
         <f t="shared" si="2"/>
-        <v>1946</v>
+        <v>1962</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="3"/>
@@ -6588,14 +6588,14 @@
       </c>
       <c r="J17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="1"/>
       <c r="M17" s="5"/>
       <c r="N17" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="11"/>
@@ -6603,14 +6603,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="13"/>
@@ -6618,14 +6618,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="15"/>
@@ -6640,18 +6640,18 @@
         <v>13</v>
       </c>
       <c r="C18" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I18" s="5">
         <f t="shared" si="3"/>
@@ -6659,14 +6659,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="11"/>
@@ -6674,14 +6674,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="13"/>
@@ -6689,14 +6689,14 @@
       </c>
       <c r="V18" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="15"/>
@@ -6711,11 +6711,11 @@
         <v>17</v>
       </c>
       <c r="C19" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E19" s="5">
         <v>303</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>1945</v>
+        <v>1961</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -6736,14 +6736,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="11"/>
@@ -6751,14 +6751,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="13"/>
@@ -6766,14 +6766,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="15"/>
@@ -6788,11 +6788,11 @@
         <v>15</v>
       </c>
       <c r="C20" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E20" s="5">
         <v>202</v>
@@ -6805,7 +6805,7 @@
       </c>
       <c r="H20" s="5">
         <f>IF((D20-E20)&lt;0,0,(D20-E20))</f>
-        <v>2046</v>
+        <v>2062</v>
       </c>
       <c r="I20" s="5">
         <f>IF((E20-D20)&lt;0,0,(E20-D20))</f>
@@ -6813,14 +6813,14 @@
       </c>
       <c r="J20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="1"/>
       <c r="M20" s="5"/>
       <c r="N20" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O20" s="5">
         <f t="shared" si="11"/>
@@ -6828,14 +6828,14 @@
       </c>
       <c r="P20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="1"/>
       <c r="S20" s="5"/>
       <c r="T20" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U20" s="5">
         <f t="shared" si="13"/>
@@ -6843,14 +6843,14 @@
       </c>
       <c r="V20" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W20" s="5"/>
       <c r="X20" s="1"/>
       <c r="Y20" s="5"/>
       <c r="Z20" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA20" s="5">
         <f t="shared" si="15"/>
@@ -6865,18 +6865,18 @@
         <v>63</v>
       </c>
       <c r="C21" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="1"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
         <f>IF((D21-E21)&lt;0,0,(D21-E21))</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I21" s="5">
         <f>IF((E21-D21)&lt;0,0,(E21-D21))</f>
@@ -6884,14 +6884,14 @@
       </c>
       <c r="J21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="1"/>
       <c r="M21" s="5"/>
       <c r="N21" s="5">
         <f t="shared" si="10"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O21" s="5">
         <f t="shared" si="11"/>
@@ -6899,14 +6899,14 @@
       </c>
       <c r="P21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q21" s="5"/>
       <c r="R21" s="1"/>
       <c r="S21" s="5"/>
       <c r="T21" s="5">
         <f t="shared" si="12"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U21" s="5">
         <f t="shared" si="13"/>
@@ -6914,21 +6914,21 @@
       </c>
       <c r="V21" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W21" s="5"/>
       <c r="X21" s="1"/>
       <c r="Y21" s="5"/>
       <c r="Z21" s="5">
         <f t="shared" si="14"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA21" s="5">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.5">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -8298,11 +8298,11 @@
         <v>15</v>
       </c>
       <c r="C43" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E43" s="5">
         <v>100</v>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="H43" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="3"/>
@@ -8323,14 +8323,14 @@
       </c>
       <c r="J43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="1"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="11"/>
@@ -8338,14 +8338,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="13"/>
@@ -8353,14 +8353,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="15"/>
@@ -8375,11 +8375,11 @@
         <v>17</v>
       </c>
       <c r="C44" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E44" s="5">
         <v>100</v>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="H44" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="3"/>
@@ -8400,14 +8400,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="11"/>
@@ -8415,14 +8415,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="13"/>
@@ -8430,14 +8430,14 @@
       </c>
       <c r="V44" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="15"/>
@@ -8452,11 +8452,11 @@
         <v>13</v>
       </c>
       <c r="C45" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E45" s="5">
         <v>100</v>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="H45" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="3"/>
@@ -8477,14 +8477,14 @@
       </c>
       <c r="J45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="1"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="11"/>
@@ -8492,14 +8492,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="13"/>
@@ -8507,14 +8507,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="15"/>
@@ -8529,11 +8529,11 @@
         <v>11</v>
       </c>
       <c r="C46" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E46" s="5">
         <v>100</v>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H46" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="3"/>
@@ -8554,14 +8554,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="11"/>
@@ -8569,14 +8569,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="13"/>
@@ -8584,14 +8584,14 @@
       </c>
       <c r="V46" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="15"/>
@@ -8606,11 +8606,11 @@
         <v>18</v>
       </c>
       <c r="C47" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E47" s="5">
         <v>100</v>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="H47" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="3"/>
@@ -8631,14 +8631,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="11"/>
@@ -8646,14 +8646,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="13"/>
@@ -8661,14 +8661,14 @@
       </c>
       <c r="V47" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="15"/>
@@ -8683,18 +8683,18 @@
         <v>14</v>
       </c>
       <c r="C48" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="2"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="3"/>
@@ -8702,14 +8702,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" si="11"/>
@@ -8717,14 +8717,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="13"/>
@@ -8732,14 +8732,14 @@
       </c>
       <c r="V48" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="15"/>
@@ -8754,11 +8754,11 @@
         <v>19</v>
       </c>
       <c r="C49" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E49" s="5">
         <v>100</v>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="H49" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I49" s="5">
         <f t="shared" si="3"/>
@@ -8779,14 +8779,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -8794,14 +8794,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U49" s="5">
         <f t="shared" si="13"/>
@@ -8809,14 +8809,14 @@
       </c>
       <c r="V49" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA49" s="5">
         <f t="shared" si="15"/>
@@ -8831,11 +8831,11 @@
         <v>20</v>
       </c>
       <c r="C50" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E50" s="5">
         <v>100</v>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="H50" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="3"/>
@@ -8856,14 +8856,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -8871,14 +8871,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="13"/>
@@ -8886,14 +8886,14 @@
       </c>
       <c r="V50" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="15"/>
@@ -8908,11 +8908,11 @@
         <v>21</v>
       </c>
       <c r="C51" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E51" s="5">
         <v>100</v>
@@ -8925,7 +8925,7 @@
       </c>
       <c r="H51" s="5">
         <f t="shared" si="2"/>
-        <v>1764</v>
+        <v>1772</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="3"/>
@@ -8933,14 +8933,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -8948,14 +8948,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="12"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="13"/>
@@ -8963,14 +8963,14 @@
       </c>
       <c r="V51" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="14"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="15"/>
@@ -8999,18 +8999,18 @@
         <v>15</v>
       </c>
       <c r="C53" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="3"/>
@@ -9018,14 +9018,14 @@
       </c>
       <c r="J53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="11"/>
@@ -9033,14 +9033,14 @@
       </c>
       <c r="P53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="13"/>
@@ -9048,14 +9048,14 @@
       </c>
       <c r="V53" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W53" s="5"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA53" s="5">
         <f t="shared" si="15"/>
@@ -9070,18 +9070,18 @@
         <v>17</v>
       </c>
       <c r="C54" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E54" s="5"/>
       <c r="F54" s="1"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I54" s="5">
         <f t="shared" si="3"/>
@@ -9089,14 +9089,14 @@
       </c>
       <c r="J54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="1"/>
       <c r="M54" s="5"/>
       <c r="N54" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O54" s="5">
         <f t="shared" si="11"/>
@@ -9104,14 +9104,14 @@
       </c>
       <c r="P54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q54" s="5"/>
       <c r="R54" s="1"/>
       <c r="S54" s="5"/>
       <c r="T54" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U54" s="5">
         <f t="shared" si="13"/>
@@ -9119,14 +9119,14 @@
       </c>
       <c r="V54" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W54" s="5"/>
       <c r="X54" s="1"/>
       <c r="Y54" s="5"/>
       <c r="Z54" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA54" s="5">
         <f t="shared" si="15"/>
@@ -9141,18 +9141,18 @@
         <v>13</v>
       </c>
       <c r="C55" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E55" s="5"/>
       <c r="F55" s="1"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="3"/>
@@ -9160,14 +9160,14 @@
       </c>
       <c r="J55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="1"/>
       <c r="M55" s="5"/>
       <c r="N55" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O55" s="5">
         <f t="shared" si="11"/>
@@ -9175,14 +9175,14 @@
       </c>
       <c r="P55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q55" s="5"/>
       <c r="R55" s="1"/>
       <c r="S55" s="5"/>
       <c r="T55" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U55" s="5">
         <f t="shared" si="13"/>
@@ -9190,14 +9190,14 @@
       </c>
       <c r="V55" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W55" s="5"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="15"/>
@@ -9212,18 +9212,18 @@
         <v>11</v>
       </c>
       <c r="C56" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="1"/>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="3"/>
@@ -9231,14 +9231,14 @@
       </c>
       <c r="J56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O56" s="5">
         <f t="shared" si="11"/>
@@ -9246,14 +9246,14 @@
       </c>
       <c r="P56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q56" s="5"/>
       <c r="R56" s="1"/>
       <c r="S56" s="5"/>
       <c r="T56" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" si="13"/>
@@ -9261,14 +9261,14 @@
       </c>
       <c r="V56" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W56" s="5"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="15"/>
@@ -9283,18 +9283,18 @@
         <v>18</v>
       </c>
       <c r="C57" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="1"/>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I57" s="5">
         <f t="shared" si="3"/>
@@ -9302,14 +9302,14 @@
       </c>
       <c r="J57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O57" s="5">
         <f t="shared" si="11"/>
@@ -9317,14 +9317,14 @@
       </c>
       <c r="P57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q57" s="5"/>
       <c r="R57" s="1"/>
       <c r="S57" s="5"/>
       <c r="T57" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U57" s="5">
         <f t="shared" si="13"/>
@@ -9332,14 +9332,14 @@
       </c>
       <c r="V57" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W57" s="5"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="15"/>
@@ -9354,18 +9354,18 @@
         <v>14</v>
       </c>
       <c r="C58" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="3"/>
@@ -9373,14 +9373,14 @@
       </c>
       <c r="J58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="11"/>
@@ -9388,14 +9388,14 @@
       </c>
       <c r="P58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q58" s="5"/>
       <c r="R58" s="1"/>
       <c r="S58" s="5"/>
       <c r="T58" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U58" s="5">
         <f t="shared" si="13"/>
@@ -9403,14 +9403,14 @@
       </c>
       <c r="V58" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA58" s="5">
         <f t="shared" si="15"/>
@@ -9425,18 +9425,18 @@
         <v>19</v>
       </c>
       <c r="C59" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" si="3"/>
@@ -9444,14 +9444,14 @@
       </c>
       <c r="J59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O59" s="5">
         <f t="shared" si="11"/>
@@ -9459,14 +9459,14 @@
       </c>
       <c r="P59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q59" s="5"/>
       <c r="R59" s="1"/>
       <c r="S59" s="5"/>
       <c r="T59" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U59" s="5">
         <f t="shared" si="13"/>
@@ -9474,14 +9474,14 @@
       </c>
       <c r="V59" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W59" s="5"/>
       <c r="X59" s="1"/>
       <c r="Y59" s="5"/>
       <c r="Z59" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="15"/>
@@ -9496,18 +9496,18 @@
         <v>20</v>
       </c>
       <c r="C60" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="3"/>
@@ -9515,14 +9515,14 @@
       </c>
       <c r="J60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O60" s="5">
         <f t="shared" si="11"/>
@@ -9530,14 +9530,14 @@
       </c>
       <c r="P60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q60" s="5"/>
       <c r="R60" s="1"/>
       <c r="S60" s="5"/>
       <c r="T60" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" si="13"/>
@@ -9545,14 +9545,14 @@
       </c>
       <c r="V60" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W60" s="5"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="15"/>
@@ -9567,18 +9567,18 @@
         <v>21</v>
       </c>
       <c r="C61" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="1"/>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="3"/>
@@ -9586,14 +9586,14 @@
       </c>
       <c r="J61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
         <f t="shared" si="10"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O61" s="5">
         <f t="shared" si="11"/>
@@ -9601,14 +9601,14 @@
       </c>
       <c r="P61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q61" s="5"/>
       <c r="R61" s="1"/>
       <c r="S61" s="5"/>
       <c r="T61" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U61" s="5">
         <f t="shared" si="13"/>
@@ -9616,14 +9616,14 @@
       </c>
       <c r="V61" s="5">
         <f>Table1[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W61" s="5"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
         <f t="shared" si="14"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA61" s="5">
         <f t="shared" si="15"/>
@@ -13736,189 +13736,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
+    <protectedRange sqref="C2:C3 C23:C31 C33:C41 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12 C14:C21 C43:C51 C53:C61" name="Textbooks"/>
     <protectedRange sqref="J2:L3 D2:F3 H5:L5 D14:F21 Q14:R21 W14:X21 D23:F31 Q23:R31 W23:X31 D33:F41 H33:I41 Q33:R41 W33:X41 D43:F51 H43:I51 Q43:R51 W43:X51 D53:F61 H53:I61 Q53:R61 W53:X61 D63:F71 H63:I71 Q63:R71 W63:X71 D73:F81 H73:I81 Q73:R81 W73:X81 D83:F91 H83:I91 Q83:R91 W83:X91 D93:F101 H93:I101 Q93:R101 W93:X101 D103:F110 H103:I110 Q103:R110 W103:X110 D112:F127 H112:I127 N127:R127 W112:X127 H14:I21 H23:I31 H6:I12 K6:L12 K33:L41 K43:L51 K53:L61 K63:L71 K73:L81 K83:L91 K93:L101 K103:L110 K112:L127 K14:L21 K23:L31 Q112:R126 P2:R2 V2:X3 N13:P126 T13:V127 J6:J127 D5:F12 N5:R12 T5:X12 N4:P4 T4:V4 J4 Z4:AA127 N3:R3 Y13" name="LAS"/>
     <protectedRange sqref="G2:I3 M2:O2 S2:U3 Y2:AA3 G112:G127 M112:M127 S112:S127 Y112:Y127 G5:G12 M5:M12 S4:S110 Y5:Y12 G14:G21 M14:M110 M3 Y14:Y110 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" name="SOURCE"/>
   </protectedRanges>
@@ -13929,15 +13749,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F63:F71 F73:F81 F83:F91 F93:F101 F103:F110 F112:F127 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12" xr:uid="{5F31E8D3-00EA-451C-BF0E-D616ABCEEE2D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13952,7 +13775,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14106,18 +13929,18 @@
         <v>8</v>
       </c>
       <c r="C3" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="1"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
         <f t="shared" ref="H3:H83" si="0">IF((D3-E3)&lt;0,0,(D3-E3))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I83" si="1">IF((E3-D3)&lt;0,0,(E3-D3))</f>
@@ -14125,14 +13948,14 @@
       </c>
       <c r="J3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="1"/>
       <c r="M3" s="5"/>
       <c r="N3" s="5">
         <f t="shared" ref="N3:N72" si="2">IF((J3-K3)&lt;0,0,(J3-K3))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O3" s="5">
         <f t="shared" ref="O3:O72" si="3">IF((K3-J3)&lt;0,0,(K3-J3))</f>
@@ -14140,14 +13963,14 @@
       </c>
       <c r="P3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q3" s="5"/>
       <c r="R3" s="1"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5">
         <f t="shared" ref="T3:T72" si="4">IF((P3-Q3)&lt;0,0,(P3-Q3))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U3" s="5">
         <f t="shared" ref="U3:U72" si="5">IF((Q3-P3)&lt;0,0,(Q3-P3))</f>
@@ -14155,14 +13978,14 @@
       </c>
       <c r="V3" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W3" s="5"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="5"/>
       <c r="Z3" s="5">
         <f t="shared" ref="Z3:Z72" si="6">IF((V3-W3)&lt;0,0,(V3-W3))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA3" s="5">
         <f t="shared" ref="AA3:AA72" si="7">IF((W3-V3)&lt;0,0,(W3-V3))</f>
@@ -14177,18 +14000,18 @@
         <v>10</v>
       </c>
       <c r="C4" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
         <f t="shared" si="0"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="1"/>
@@ -14196,14 +14019,14 @@
       </c>
       <c r="J4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="1"/>
       <c r="M4" s="5"/>
       <c r="N4" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O4" s="5">
         <f t="shared" si="3"/>
@@ -14211,14 +14034,14 @@
       </c>
       <c r="P4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q4" s="5"/>
       <c r="R4" s="1"/>
       <c r="S4" s="5"/>
       <c r="T4" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U4" s="5">
         <f t="shared" si="5"/>
@@ -14226,14 +14049,14 @@
       </c>
       <c r="V4" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W4" s="5"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="5"/>
       <c r="Z4" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA4" s="5">
         <f t="shared" si="7"/>
@@ -14248,18 +14071,18 @@
         <v>11</v>
       </c>
       <c r="C5" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="1"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5">
         <f t="shared" si="0"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="1"/>
@@ -14267,14 +14090,14 @@
       </c>
       <c r="J5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="1"/>
       <c r="M5" s="5"/>
       <c r="N5" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O5" s="5">
         <f t="shared" si="3"/>
@@ -14282,14 +14105,14 @@
       </c>
       <c r="P5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q5" s="5"/>
       <c r="R5" s="1"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U5" s="5">
         <f t="shared" si="5"/>
@@ -14297,14 +14120,14 @@
       </c>
       <c r="V5" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W5" s="5"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="5"/>
       <c r="Z5" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA5" s="5">
         <f t="shared" si="7"/>
@@ -14319,18 +14142,18 @@
         <v>12</v>
       </c>
       <c r="C6" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="1"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
         <f t="shared" si="0"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="1"/>
@@ -14338,14 +14161,14 @@
       </c>
       <c r="J6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="1"/>
       <c r="M6" s="5"/>
       <c r="N6" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O6" s="5">
         <f t="shared" si="3"/>
@@ -14353,14 +14176,14 @@
       </c>
       <c r="P6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="1"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U6" s="5">
         <f t="shared" si="5"/>
@@ -14368,14 +14191,14 @@
       </c>
       <c r="V6" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W6" s="5"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="5"/>
       <c r="Z6" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="7"/>
@@ -14390,18 +14213,18 @@
         <v>13</v>
       </c>
       <c r="C7" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="1"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5">
         <f t="shared" si="0"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="1"/>
@@ -14409,14 +14232,14 @@
       </c>
       <c r="J7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="1"/>
       <c r="M7" s="5"/>
       <c r="N7" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O7" s="5">
         <f t="shared" si="3"/>
@@ -14424,14 +14247,14 @@
       </c>
       <c r="P7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="1"/>
       <c r="S7" s="5"/>
       <c r="T7" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U7" s="5">
         <f t="shared" si="5"/>
@@ -14439,14 +14262,14 @@
       </c>
       <c r="V7" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W7" s="5"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="5"/>
       <c r="Z7" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA7" s="5">
         <f t="shared" si="7"/>
@@ -14461,18 +14284,18 @@
         <v>15</v>
       </c>
       <c r="C8" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="1"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
         <f>IF((D8-E8)&lt;0,0,(D8-E8))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I8" s="5">
         <f>IF((E8-D8)&lt;0,0,(E8-D8))</f>
@@ -14480,14 +14303,14 @@
       </c>
       <c r="J8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="1"/>
       <c r="M8" s="5"/>
       <c r="N8" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O8" s="5">
         <f t="shared" si="3"/>
@@ -14495,14 +14318,14 @@
       </c>
       <c r="P8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="1"/>
       <c r="S8" s="5"/>
       <c r="T8" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U8" s="5">
         <f t="shared" si="5"/>
@@ -14510,14 +14333,14 @@
       </c>
       <c r="V8" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W8" s="5"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="5"/>
       <c r="Z8" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA8" s="5">
         <f t="shared" si="7"/>
@@ -14532,18 +14355,18 @@
         <v>17</v>
       </c>
       <c r="C9" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
         <f>IF((D9-E9)&lt;0,0,(D9-E9))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I9" s="5">
         <f>IF((E9-D9)&lt;0,0,(E9-D9))</f>
@@ -14551,14 +14374,14 @@
       </c>
       <c r="J9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="1"/>
       <c r="M9" s="5"/>
       <c r="N9" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O9" s="5">
         <f t="shared" si="3"/>
@@ -14566,14 +14389,14 @@
       </c>
       <c r="P9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="1"/>
       <c r="S9" s="5"/>
       <c r="T9" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U9" s="5">
         <f t="shared" si="5"/>
@@ -14581,14 +14404,14 @@
       </c>
       <c r="V9" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W9" s="5"/>
       <c r="X9" s="1"/>
       <c r="Y9" s="5"/>
       <c r="Z9" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA9" s="5">
         <f t="shared" si="7"/>
@@ -14603,18 +14426,18 @@
         <v>63</v>
       </c>
       <c r="C10" s="1">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
         <f>IF((D10-E10)&lt;0,0,(D10-E10))</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="I10" s="5">
         <f>IF((E10-D10)&lt;0,0,(E10-D10))</f>
@@ -14622,14 +14445,14 @@
       </c>
       <c r="J10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="1"/>
       <c r="M10" s="5"/>
       <c r="N10" s="5">
         <f t="shared" si="2"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="O10" s="5">
         <f t="shared" si="3"/>
@@ -14637,14 +14460,14 @@
       </c>
       <c r="P10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="1"/>
       <c r="S10" s="5"/>
       <c r="T10" s="5">
         <f t="shared" si="4"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="U10" s="5">
         <f t="shared" si="5"/>
@@ -14652,14 +14475,14 @@
       </c>
       <c r="V10" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="W10" s="5"/>
       <c r="X10" s="1"/>
       <c r="Y10" s="5"/>
       <c r="Z10" s="5">
         <f t="shared" si="6"/>
-        <v>1712</v>
+        <v>1688</v>
       </c>
       <c r="AA10" s="5">
         <f t="shared" si="7"/>
@@ -14675,18 +14498,18 @@
         <v>8</v>
       </c>
       <c r="C12" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
         <f t="shared" si="0"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="1"/>
@@ -14694,14 +14517,14 @@
       </c>
       <c r="J12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="1"/>
       <c r="M12" s="5"/>
       <c r="N12" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O12" s="5">
         <f t="shared" si="3"/>
@@ -14709,14 +14532,14 @@
       </c>
       <c r="P12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="1"/>
       <c r="S12" s="5"/>
       <c r="T12" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U12" s="5">
         <f t="shared" si="5"/>
@@ -14724,14 +14547,14 @@
       </c>
       <c r="V12" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W12" s="5"/>
       <c r="X12" s="1"/>
       <c r="Y12" s="5"/>
       <c r="Z12" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA12" s="5">
         <f t="shared" si="7"/>
@@ -14746,18 +14569,18 @@
         <v>10</v>
       </c>
       <c r="C13" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="1"/>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
         <f t="shared" si="0"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="1"/>
@@ -14765,14 +14588,14 @@
       </c>
       <c r="J13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="1"/>
       <c r="M13" s="5"/>
       <c r="N13" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O13" s="5">
         <f t="shared" si="3"/>
@@ -14780,14 +14603,14 @@
       </c>
       <c r="P13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="1"/>
       <c r="S13" s="5"/>
       <c r="T13" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U13" s="5">
         <f t="shared" si="5"/>
@@ -14795,14 +14618,14 @@
       </c>
       <c r="V13" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W13" s="5"/>
       <c r="X13" s="1"/>
       <c r="Y13" s="5"/>
       <c r="Z13" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA13" s="5">
         <f t="shared" si="7"/>
@@ -14817,18 +14640,18 @@
         <v>11</v>
       </c>
       <c r="C14" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="1"/>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
         <f t="shared" si="0"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I14" s="5">
         <f t="shared" si="1"/>
@@ -14836,14 +14659,14 @@
       </c>
       <c r="J14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="1"/>
       <c r="M14" s="5"/>
       <c r="N14" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O14" s="5">
         <f t="shared" si="3"/>
@@ -14851,14 +14674,14 @@
       </c>
       <c r="P14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="1"/>
       <c r="S14" s="5"/>
       <c r="T14" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U14" s="5">
         <f t="shared" si="5"/>
@@ -14866,14 +14689,14 @@
       </c>
       <c r="V14" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W14" s="5"/>
       <c r="X14" s="1"/>
       <c r="Y14" s="5"/>
       <c r="Z14" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA14" s="5">
         <f t="shared" si="7"/>
@@ -14888,18 +14711,18 @@
         <v>12</v>
       </c>
       <c r="C15" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="1"/>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I15" s="5">
         <f t="shared" si="1"/>
@@ -14907,7 +14730,7 @@
       </c>
       <c r="J15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K15" s="5">
         <v>282</v>
@@ -14920,7 +14743,7 @@
       </c>
       <c r="N15" s="5">
         <f t="shared" si="2"/>
-        <v>1966</v>
+        <v>1982</v>
       </c>
       <c r="O15" s="5">
         <f t="shared" si="3"/>
@@ -14928,14 +14751,14 @@
       </c>
       <c r="P15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="1"/>
       <c r="S15" s="5"/>
       <c r="T15" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U15" s="5">
         <f t="shared" si="5"/>
@@ -14943,14 +14766,14 @@
       </c>
       <c r="V15" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W15" s="5"/>
       <c r="X15" s="1"/>
       <c r="Y15" s="5"/>
       <c r="Z15" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA15" s="5">
         <f t="shared" si="7"/>
@@ -14965,18 +14788,18 @@
         <v>13</v>
       </c>
       <c r="C16" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="1"/>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
         <f t="shared" si="0"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="1"/>
@@ -14984,14 +14807,14 @@
       </c>
       <c r="J16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="1"/>
       <c r="M16" s="5"/>
       <c r="N16" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O16" s="5">
         <f t="shared" si="3"/>
@@ -14999,14 +14822,14 @@
       </c>
       <c r="P16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="1"/>
       <c r="S16" s="5"/>
       <c r="T16" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U16" s="5">
         <f t="shared" si="5"/>
@@ -15014,14 +14837,14 @@
       </c>
       <c r="V16" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W16" s="5"/>
       <c r="X16" s="1"/>
       <c r="Y16" s="5"/>
       <c r="Z16" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA16" s="5">
         <f t="shared" si="7"/>
@@ -15036,18 +14859,18 @@
         <v>17</v>
       </c>
       <c r="C17" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="1"/>
       <c r="G17" s="5"/>
       <c r="H17" s="5">
         <f>IF((D17-E17)&lt;0,0,(D17-E17))</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I17" s="5">
         <f>IF((E17-D17)&lt;0,0,(E17-D17))</f>
@@ -15055,7 +14878,7 @@
       </c>
       <c r="J17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K17" s="5">
         <v>282</v>
@@ -15068,7 +14891,7 @@
       </c>
       <c r="N17" s="5">
         <f t="shared" si="2"/>
-        <v>1966</v>
+        <v>1982</v>
       </c>
       <c r="O17" s="5">
         <f t="shared" si="3"/>
@@ -15076,14 +14899,14 @@
       </c>
       <c r="P17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q17" s="5"/>
       <c r="R17" s="1"/>
       <c r="S17" s="5"/>
       <c r="T17" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U17" s="5">
         <f t="shared" si="5"/>
@@ -15091,14 +14914,14 @@
       </c>
       <c r="V17" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W17" s="5"/>
       <c r="X17" s="1"/>
       <c r="Y17" s="5"/>
       <c r="Z17" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA17" s="5">
         <f t="shared" si="7"/>
@@ -15113,18 +14936,18 @@
         <v>15</v>
       </c>
       <c r="C18" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="1"/>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
         <f>IF((D18-E18)&lt;0,0,(D18-E18))</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I18" s="5">
         <f>IF((E18-D18)&lt;0,0,(E18-D18))</f>
@@ -15132,14 +14955,14 @@
       </c>
       <c r="J18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="1"/>
       <c r="M18" s="5"/>
       <c r="N18" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O18" s="5">
         <f t="shared" si="3"/>
@@ -15147,14 +14970,14 @@
       </c>
       <c r="P18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="1"/>
       <c r="S18" s="5"/>
       <c r="T18" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U18" s="5">
         <f t="shared" si="5"/>
@@ -15162,14 +14985,14 @@
       </c>
       <c r="V18" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W18" s="5"/>
       <c r="X18" s="1"/>
       <c r="Y18" s="5"/>
       <c r="Z18" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA18" s="5">
         <f t="shared" si="7"/>
@@ -15184,18 +15007,18 @@
         <v>63</v>
       </c>
       <c r="C19" s="1">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="1"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
         <f>IF((D19-E19)&lt;0,0,(D19-E19))</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="I19" s="5">
         <f>IF((E19-D19)&lt;0,0,(E19-D19))</f>
@@ -15203,14 +15026,14 @@
       </c>
       <c r="J19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="1"/>
       <c r="M19" s="5"/>
       <c r="N19" s="5">
         <f t="shared" si="2"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="O19" s="5">
         <f t="shared" si="3"/>
@@ -15218,14 +15041,14 @@
       </c>
       <c r="P19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="1"/>
       <c r="S19" s="5"/>
       <c r="T19" s="5">
         <f t="shared" si="4"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="U19" s="5">
         <f t="shared" si="5"/>
@@ -15233,14 +15056,14 @@
       </c>
       <c r="V19" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="W19" s="5"/>
       <c r="X19" s="1"/>
       <c r="Y19" s="5"/>
       <c r="Z19" s="5">
         <f t="shared" si="6"/>
-        <v>2248</v>
+        <v>2264</v>
       </c>
       <c r="AA19" s="5">
         <f t="shared" si="7"/>
@@ -16678,18 +16501,18 @@
         <v>15</v>
       </c>
       <c r="C43" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="1"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I43" s="5">
         <f t="shared" si="1"/>
@@ -16697,7 +16520,7 @@
       </c>
       <c r="J43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K43" s="5">
         <v>238</v>
@@ -16710,7 +16533,7 @@
       </c>
       <c r="N43" s="5">
         <f t="shared" si="2"/>
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="O43" s="5">
         <f t="shared" si="3"/>
@@ -16718,14 +16541,14 @@
       </c>
       <c r="P43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="1"/>
       <c r="S43" s="5"/>
       <c r="T43" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U43" s="5">
         <f t="shared" si="5"/>
@@ -16733,14 +16556,14 @@
       </c>
       <c r="V43" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W43" s="5"/>
       <c r="X43" s="1"/>
       <c r="Y43" s="5"/>
       <c r="Z43" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA43" s="5">
         <f t="shared" si="7"/>
@@ -16755,18 +16578,18 @@
         <v>17</v>
       </c>
       <c r="C44" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="1"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I44" s="5">
         <f t="shared" si="1"/>
@@ -16774,14 +16597,14 @@
       </c>
       <c r="J44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="1"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5">
         <f t="shared" si="2"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O44" s="5">
         <f t="shared" si="3"/>
@@ -16789,14 +16612,14 @@
       </c>
       <c r="P44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="1"/>
       <c r="S44" s="5"/>
       <c r="T44" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U44" s="5">
         <f t="shared" si="5"/>
@@ -16804,14 +16627,14 @@
       </c>
       <c r="V44" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W44" s="5"/>
       <c r="X44" s="1"/>
       <c r="Y44" s="5"/>
       <c r="Z44" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA44" s="5">
         <f t="shared" si="7"/>
@@ -16826,18 +16649,18 @@
         <v>13</v>
       </c>
       <c r="C45" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="1"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I45" s="5">
         <f t="shared" si="1"/>
@@ -16845,7 +16668,7 @@
       </c>
       <c r="J45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K45" s="5">
         <v>238</v>
@@ -16858,7 +16681,7 @@
       </c>
       <c r="N45" s="5">
         <f t="shared" si="2"/>
-        <v>1626</v>
+        <v>1634</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" si="3"/>
@@ -16866,14 +16689,14 @@
       </c>
       <c r="P45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q45" s="5"/>
       <c r="R45" s="1"/>
       <c r="S45" s="5"/>
       <c r="T45" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" si="5"/>
@@ -16881,14 +16704,14 @@
       </c>
       <c r="V45" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W45" s="5"/>
       <c r="X45" s="1"/>
       <c r="Y45" s="5"/>
       <c r="Z45" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA45" s="5">
         <f t="shared" si="7"/>
@@ -16903,18 +16726,18 @@
         <v>11</v>
       </c>
       <c r="C46" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="1"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I46" s="5">
         <f t="shared" si="1"/>
@@ -16922,14 +16745,14 @@
       </c>
       <c r="J46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="1"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5">
         <f t="shared" si="2"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O46" s="5">
         <f t="shared" si="3"/>
@@ -16937,14 +16760,14 @@
       </c>
       <c r="P46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q46" s="5"/>
       <c r="R46" s="1"/>
       <c r="S46" s="5"/>
       <c r="T46" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U46" s="5">
         <f t="shared" si="5"/>
@@ -16952,14 +16775,14 @@
       </c>
       <c r="V46" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W46" s="5"/>
       <c r="X46" s="1"/>
       <c r="Y46" s="5"/>
       <c r="Z46" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA46" s="5">
         <f t="shared" si="7"/>
@@ -16974,18 +16797,18 @@
         <v>18</v>
       </c>
       <c r="C47" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="1"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I47" s="5">
         <f t="shared" si="1"/>
@@ -16993,14 +16816,14 @@
       </c>
       <c r="J47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="1"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5">
         <f t="shared" si="2"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O47" s="5">
         <f t="shared" si="3"/>
@@ -17008,14 +16831,14 @@
       </c>
       <c r="P47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="1"/>
       <c r="S47" s="5"/>
       <c r="T47" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U47" s="5">
         <f t="shared" si="5"/>
@@ -17023,14 +16846,14 @@
       </c>
       <c r="V47" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W47" s="5"/>
       <c r="X47" s="1"/>
       <c r="Y47" s="5"/>
       <c r="Z47" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA47" s="5">
         <f t="shared" si="7"/>
@@ -17045,18 +16868,18 @@
         <v>14</v>
       </c>
       <c r="C48" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="1"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I48" s="5">
         <f t="shared" si="1"/>
@@ -17064,14 +16887,14 @@
       </c>
       <c r="J48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f t="shared" ref="N48:N53" si="10">IF((J48-K48)&lt;0,0,(J48-K48))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" ref="O48:O53" si="11">IF((K48-J48)&lt;0,0,(K48-J48))</f>
@@ -17079,14 +16902,14 @@
       </c>
       <c r="P48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="1"/>
       <c r="S48" s="5"/>
       <c r="T48" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" si="5"/>
@@ -17094,14 +16917,14 @@
       </c>
       <c r="V48" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W48" s="5"/>
       <c r="X48" s="1"/>
       <c r="Y48" s="5"/>
       <c r="Z48" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA48" s="5">
         <f t="shared" si="7"/>
@@ -17115,19 +16938,19 @@
       <c r="B49" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="5">
-        <v>233</v>
+      <c r="C49" s="1">
+        <v>234</v>
       </c>
       <c r="D49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="1"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
         <f>IF((D49-E49)&lt;0,0,(D49-E49))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I49" s="5">
         <f>IF((E49-D49)&lt;0,0,(E49-D49))</f>
@@ -17135,14 +16958,14 @@
       </c>
       <c r="J49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="1"/>
       <c r="M49" s="5"/>
       <c r="N49" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O49" s="5">
         <f t="shared" si="11"/>
@@ -17150,14 +16973,14 @@
       </c>
       <c r="P49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q49" s="5"/>
       <c r="R49" s="1"/>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f>IF((P49-Q49)&lt;0,0,(P49-Q49))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U49" s="5">
         <f>IF((Q49-P49)&lt;0,0,(Q49-P49))</f>
@@ -17165,14 +16988,14 @@
       </c>
       <c r="V49" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W49" s="5"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="5"/>
       <c r="Z49" s="5">
         <f>IF((V49-W49)&lt;0,0,(V49-W49))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA49" s="5">
         <f>IF((W49-V49)&lt;0,0,(W49-V49))</f>
@@ -17187,18 +17010,18 @@
         <v>89</v>
       </c>
       <c r="C50" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="1"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I50" s="5">
         <f t="shared" si="1"/>
@@ -17206,14 +17029,14 @@
       </c>
       <c r="J50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="1"/>
       <c r="M50" s="5"/>
       <c r="N50" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O50" s="5">
         <f t="shared" si="11"/>
@@ -17221,14 +17044,14 @@
       </c>
       <c r="P50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="1"/>
       <c r="S50" s="5"/>
       <c r="T50" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U50" s="5">
         <f t="shared" si="5"/>
@@ -17236,14 +17059,14 @@
       </c>
       <c r="V50" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W50" s="5"/>
       <c r="X50" s="1"/>
       <c r="Y50" s="5"/>
       <c r="Z50" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA50" s="5">
         <f t="shared" si="7"/>
@@ -17258,18 +17081,18 @@
         <v>20</v>
       </c>
       <c r="C51" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="1"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I51" s="5">
         <f t="shared" si="1"/>
@@ -17277,14 +17100,14 @@
       </c>
       <c r="J51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="1"/>
       <c r="M51" s="5"/>
       <c r="N51" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O51" s="5">
         <f t="shared" si="11"/>
@@ -17292,14 +17115,14 @@
       </c>
       <c r="P51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="1"/>
       <c r="S51" s="5"/>
       <c r="T51" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U51" s="5">
         <f t="shared" si="5"/>
@@ -17307,14 +17130,14 @@
       </c>
       <c r="V51" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W51" s="5"/>
       <c r="X51" s="1"/>
       <c r="Y51" s="5"/>
       <c r="Z51" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA51" s="5">
         <f t="shared" si="7"/>
@@ -17328,19 +17151,19 @@
       <c r="B52" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="5">
-        <v>233</v>
+      <c r="C52" s="1">
+        <v>234</v>
       </c>
       <c r="D52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="1"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
         <f>IF((D52-E52)&lt;0,0,(D52-E52))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I52" s="5">
         <f>IF((E52-D52)&lt;0,0,(E52-D52))</f>
@@ -17348,14 +17171,14 @@
       </c>
       <c r="J52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="1"/>
       <c r="M52" s="5"/>
       <c r="N52" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O52" s="5">
         <f t="shared" si="11"/>
@@ -17363,14 +17186,14 @@
       </c>
       <c r="P52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q52" s="5"/>
       <c r="R52" s="1"/>
       <c r="S52" s="5"/>
       <c r="T52" s="5">
         <f>IF((P52-Q52)&lt;0,0,(P52-Q52))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U52" s="5">
         <f>IF((Q52-P52)&lt;0,0,(Q52-P52))</f>
@@ -17378,14 +17201,14 @@
       </c>
       <c r="V52" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W52" s="5"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="5"/>
       <c r="Z52" s="5">
         <f>IF((V52-W52)&lt;0,0,(V52-W52))</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA52" s="5">
         <f>IF((W52-V52)&lt;0,0,(W52-V52))</f>
@@ -17400,18 +17223,18 @@
         <v>91</v>
       </c>
       <c r="C53" s="1">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="1"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
         <f t="shared" si="0"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="I53" s="5">
         <f t="shared" si="1"/>
@@ -17419,14 +17242,14 @@
       </c>
       <c r="J53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="1"/>
       <c r="M53" s="5"/>
       <c r="N53" s="5">
         <f t="shared" si="10"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="O53" s="5">
         <f t="shared" si="11"/>
@@ -17434,14 +17257,14 @@
       </c>
       <c r="P53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="Q53" s="5"/>
       <c r="R53" s="1"/>
       <c r="S53" s="5"/>
       <c r="T53" s="5">
         <f t="shared" si="4"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="U53" s="5">
         <f t="shared" si="5"/>
@@ -17449,14 +17272,14 @@
       </c>
       <c r="V53" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="W53" s="5"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="5"/>
       <c r="Z53" s="5">
         <f t="shared" si="6"/>
-        <v>1864</v>
+        <v>1872</v>
       </c>
       <c r="AA53" s="5">
         <f t="shared" si="7"/>
@@ -17472,11 +17295,11 @@
         <v>15</v>
       </c>
       <c r="C55" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D55" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E55" s="5">
         <v>39</v>
@@ -17489,7 +17312,7 @@
       </c>
       <c r="H55" s="5">
         <f t="shared" si="0"/>
-        <v>2257</v>
+        <v>2249</v>
       </c>
       <c r="I55" s="5">
         <f t="shared" si="1"/>
@@ -17497,7 +17320,7 @@
       </c>
       <c r="J55" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K55" s="5">
         <v>180</v>
@@ -17510,7 +17333,7 @@
       </c>
       <c r="N55" s="5">
         <f t="shared" si="2"/>
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="O55" s="5">
         <f t="shared" si="3"/>
@@ -17518,7 +17341,7 @@
       </c>
       <c r="P55" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q55" s="5">
         <v>120</v>
@@ -17531,7 +17354,7 @@
       </c>
       <c r="T55" s="5">
         <f t="shared" si="4"/>
-        <v>2176</v>
+        <v>2168</v>
       </c>
       <c r="U55" s="5">
         <f t="shared" si="5"/>
@@ -17539,14 +17362,14 @@
       </c>
       <c r="V55" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W55" s="5"/>
       <c r="X55" s="1"/>
       <c r="Y55" s="5"/>
       <c r="Z55" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA55" s="5">
         <f t="shared" si="7"/>
@@ -17561,11 +17384,11 @@
         <v>17</v>
       </c>
       <c r="C56" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D56" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E56" s="5">
         <v>182</v>
@@ -17578,7 +17401,7 @@
       </c>
       <c r="H56" s="5">
         <f t="shared" si="0"/>
-        <v>2114</v>
+        <v>2106</v>
       </c>
       <c r="I56" s="5">
         <f t="shared" si="1"/>
@@ -17586,14 +17409,14 @@
       </c>
       <c r="J56" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="1"/>
       <c r="M56" s="5"/>
       <c r="N56" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O56" s="5">
         <f t="shared" si="3"/>
@@ -17601,7 +17424,7 @@
       </c>
       <c r="P56" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q56" s="5">
         <v>360</v>
@@ -17614,7 +17437,7 @@
       </c>
       <c r="T56" s="5">
         <f t="shared" si="4"/>
-        <v>1936</v>
+        <v>1928</v>
       </c>
       <c r="U56" s="5">
         <f t="shared" si="5"/>
@@ -17622,14 +17445,14 @@
       </c>
       <c r="V56" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W56" s="5"/>
       <c r="X56" s="1"/>
       <c r="Y56" s="5"/>
       <c r="Z56" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA56" s="5">
         <f t="shared" si="7"/>
@@ -17644,11 +17467,11 @@
         <v>13</v>
       </c>
       <c r="C57" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D57" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E57" s="5">
         <v>143</v>
@@ -17661,7 +17484,7 @@
       </c>
       <c r="H57" s="5">
         <f t="shared" si="0"/>
-        <v>2153</v>
+        <v>2145</v>
       </c>
       <c r="I57" s="5">
         <f t="shared" si="1"/>
@@ -17669,14 +17492,14 @@
       </c>
       <c r="J57" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="1"/>
       <c r="M57" s="5"/>
       <c r="N57" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O57" s="5">
         <f t="shared" si="3"/>
@@ -17684,7 +17507,7 @@
       </c>
       <c r="P57" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q57" s="5">
         <v>540</v>
@@ -17697,7 +17520,7 @@
       </c>
       <c r="T57" s="5">
         <f t="shared" si="4"/>
-        <v>1756</v>
+        <v>1748</v>
       </c>
       <c r="U57" s="5">
         <f t="shared" si="5"/>
@@ -17705,14 +17528,14 @@
       </c>
       <c r="V57" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W57" s="5"/>
       <c r="X57" s="1"/>
       <c r="Y57" s="5"/>
       <c r="Z57" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA57" s="5">
         <f t="shared" si="7"/>
@@ -17727,18 +17550,18 @@
         <v>11</v>
       </c>
       <c r="C58" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D58" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E58" s="5"/>
       <c r="F58" s="1"/>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I58" s="5">
         <f t="shared" si="1"/>
@@ -17746,14 +17569,14 @@
       </c>
       <c r="J58" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="1"/>
       <c r="M58" s="5"/>
       <c r="N58" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O58" s="5">
         <f t="shared" si="3"/>
@@ -17761,7 +17584,7 @@
       </c>
       <c r="P58" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q58" s="5">
         <v>240</v>
@@ -17774,7 +17597,7 @@
       </c>
       <c r="T58" s="5">
         <f t="shared" si="4"/>
-        <v>2056</v>
+        <v>2048</v>
       </c>
       <c r="U58" s="5">
         <f t="shared" si="5"/>
@@ -17782,14 +17605,14 @@
       </c>
       <c r="V58" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W58" s="5"/>
       <c r="X58" s="1"/>
       <c r="Y58" s="5"/>
       <c r="Z58" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA58" s="5">
         <f t="shared" si="7"/>
@@ -17804,18 +17627,18 @@
         <v>18</v>
       </c>
       <c r="C59" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D59" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="1"/>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I59" s="5">
         <f t="shared" si="1"/>
@@ -17823,14 +17646,14 @@
       </c>
       <c r="J59" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="1"/>
       <c r="M59" s="5"/>
       <c r="N59" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O59" s="5">
         <f t="shared" si="3"/>
@@ -17838,7 +17661,7 @@
       </c>
       <c r="P59" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q59" s="5">
         <v>360</v>
@@ -17851,7 +17674,7 @@
       </c>
       <c r="T59" s="5">
         <f t="shared" si="4"/>
-        <v>1936</v>
+        <v>1928</v>
       </c>
       <c r="U59" s="5">
         <f t="shared" si="5"/>
@@ -17859,7 +17682,7 @@
       </c>
       <c r="V59" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W59" s="5">
         <v>420</v>
@@ -17872,7 +17695,7 @@
       </c>
       <c r="Z59" s="5">
         <f t="shared" si="6"/>
-        <v>1876</v>
+        <v>1868</v>
       </c>
       <c r="AA59" s="5">
         <f t="shared" si="7"/>
@@ -17887,18 +17710,18 @@
         <v>14</v>
       </c>
       <c r="C60" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D60" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="1"/>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I60" s="5">
         <f t="shared" si="1"/>
@@ -17906,14 +17729,14 @@
       </c>
       <c r="J60" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="1"/>
       <c r="M60" s="5"/>
       <c r="N60" s="5">
         <f t="shared" si="2"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O60" s="5">
         <f t="shared" si="3"/>
@@ -17921,7 +17744,7 @@
       </c>
       <c r="P60" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q60" s="5">
         <v>240</v>
@@ -17934,7 +17757,7 @@
       </c>
       <c r="T60" s="5">
         <f t="shared" si="4"/>
-        <v>2056</v>
+        <v>2048</v>
       </c>
       <c r="U60" s="5">
         <f t="shared" si="5"/>
@@ -17942,14 +17765,14 @@
       </c>
       <c r="V60" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W60" s="5"/>
       <c r="X60" s="1"/>
       <c r="Y60" s="5"/>
       <c r="Z60" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA60" s="5">
         <f t="shared" si="7"/>
@@ -17963,12 +17786,12 @@
       <c r="B61" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="5">
-        <v>287</v>
+      <c r="C61" s="1">
+        <v>286</v>
       </c>
       <c r="D61" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E61" s="5"/>
       <c r="F61" s="1">
@@ -17977,7 +17800,7 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5">
         <f>IF((D61-E61)&lt;0,0,(D61-E61))</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I61" s="5">
         <f>IF((E61-D61)&lt;0,0,(E61-D61))</f>
@@ -17985,14 +17808,14 @@
       </c>
       <c r="J61" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="1"/>
       <c r="M61" s="5"/>
       <c r="N61" s="5">
         <f t="shared" ref="N61:N65" si="12">IF((J61-K61)&lt;0,0,(J61-K61))</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O61" s="5">
         <f t="shared" ref="O61:O65" si="13">IF((K61-J61)&lt;0,0,(K61-J61))</f>
@@ -18000,7 +17823,7 @@
       </c>
       <c r="P61" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q61" s="5">
         <v>240</v>
@@ -18013,7 +17836,7 @@
       </c>
       <c r="T61" s="5">
         <f>IF((P61-Q61)&lt;0,0,(P61-Q61))</f>
-        <v>2056</v>
+        <v>2048</v>
       </c>
       <c r="U61" s="5">
         <f>IF((Q61-P61)&lt;0,0,(Q61-P61))</f>
@@ -18021,14 +17844,14 @@
       </c>
       <c r="V61" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W61" s="5"/>
       <c r="X61" s="1"/>
       <c r="Y61" s="5"/>
       <c r="Z61" s="5">
         <f>IF((V61-W61)&lt;0,0,(V61-W61))</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA61" s="5">
         <f>IF((W61-V61)&lt;0,0,(W61-V61))</f>
@@ -18043,18 +17866,18 @@
         <v>89</v>
       </c>
       <c r="C62" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D62" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="1"/>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I62" s="5">
         <f t="shared" si="1"/>
@@ -18062,14 +17885,14 @@
       </c>
       <c r="J62" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="1"/>
       <c r="M62" s="5"/>
       <c r="N62" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O62" s="5">
         <f t="shared" si="13"/>
@@ -18077,7 +17900,7 @@
       </c>
       <c r="P62" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q62" s="5">
         <v>420</v>
@@ -18090,7 +17913,7 @@
       </c>
       <c r="T62" s="5">
         <f t="shared" si="4"/>
-        <v>1876</v>
+        <v>1868</v>
       </c>
       <c r="U62" s="5">
         <f t="shared" si="5"/>
@@ -18098,14 +17921,14 @@
       </c>
       <c r="V62" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W62" s="5"/>
       <c r="X62" s="1"/>
       <c r="Y62" s="5"/>
       <c r="Z62" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA62" s="5">
         <f t="shared" si="7"/>
@@ -18120,18 +17943,18 @@
         <v>20</v>
       </c>
       <c r="C63" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D63" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E63" s="5"/>
       <c r="F63" s="1"/>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I63" s="5">
         <f t="shared" si="1"/>
@@ -18139,14 +17962,14 @@
       </c>
       <c r="J63" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="1"/>
       <c r="M63" s="5"/>
       <c r="N63" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O63" s="5">
         <f t="shared" si="13"/>
@@ -18154,14 +17977,14 @@
       </c>
       <c r="P63" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q63" s="5"/>
       <c r="R63" s="1"/>
       <c r="S63" s="5"/>
       <c r="T63" s="5">
         <f t="shared" si="4"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="U63" s="5">
         <f t="shared" si="5"/>
@@ -18169,14 +17992,14 @@
       </c>
       <c r="V63" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W63" s="5"/>
       <c r="X63" s="1"/>
       <c r="Y63" s="5"/>
       <c r="Z63" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA63" s="5">
         <f t="shared" si="7"/>
@@ -18190,19 +18013,19 @@
       <c r="B64" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C64" s="5">
-        <v>287</v>
+      <c r="C64" s="1">
+        <v>286</v>
       </c>
       <c r="D64" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E64" s="5"/>
       <c r="F64" s="1"/>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
         <f>IF((D64-E64)&lt;0,0,(D64-E64))</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I64" s="5">
         <f>IF((E64-D64)&lt;0,0,(E64-D64))</f>
@@ -18210,14 +18033,14 @@
       </c>
       <c r="J64" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="1"/>
       <c r="M64" s="5"/>
       <c r="N64" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O64" s="5">
         <f t="shared" si="13"/>
@@ -18225,7 +18048,7 @@
       </c>
       <c r="P64" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q64" s="5">
         <v>180</v>
@@ -18238,7 +18061,7 @@
       </c>
       <c r="T64" s="5">
         <f>IF((P64-Q64)&lt;0,0,(P64-Q64))</f>
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="U64" s="5">
         <f>IF((Q64-P64)&lt;0,0,(Q64-P64))</f>
@@ -18246,14 +18069,14 @@
       </c>
       <c r="V64" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W64" s="5"/>
       <c r="X64" s="1"/>
       <c r="Y64" s="5"/>
       <c r="Z64" s="5">
         <f>IF((V64-W64)&lt;0,0,(V64-W64))</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA64" s="5">
         <f>IF((W64-V64)&lt;0,0,(W64-V64))</f>
@@ -18268,18 +18091,18 @@
         <v>91</v>
       </c>
       <c r="C65" s="1">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D65" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="E65" s="5"/>
       <c r="F65" s="1"/>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
         <f t="shared" si="0"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="I65" s="5">
         <f t="shared" si="1"/>
@@ -18287,14 +18110,14 @@
       </c>
       <c r="J65" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="1"/>
       <c r="M65" s="5"/>
       <c r="N65" s="5">
         <f t="shared" si="12"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="O65" s="5">
         <f t="shared" si="13"/>
@@ -18302,7 +18125,7 @@
       </c>
       <c r="P65" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="Q65" s="5">
         <v>180</v>
@@ -18315,7 +18138,7 @@
       </c>
       <c r="T65" s="5">
         <f t="shared" si="4"/>
-        <v>2116</v>
+        <v>2108</v>
       </c>
       <c r="U65" s="5">
         <f t="shared" si="5"/>
@@ -18323,14 +18146,14 @@
       </c>
       <c r="V65" s="5">
         <f>Table14[[#This Row],[Enrolment S.Y. 2025-2026 ]]*8</f>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="W65" s="5"/>
       <c r="X65" s="1"/>
       <c r="Y65" s="5"/>
       <c r="Z65" s="5">
         <f t="shared" si="6"/>
-        <v>2296</v>
+        <v>2288</v>
       </c>
       <c r="AA65" s="5">
         <f t="shared" si="7"/>
@@ -22441,189 +22264,9 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
-    <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
+    <protectedRange sqref="C21:C29 C31:C41 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101 C2:C10 C12:C19 C43:C53 C55:C65" name="Textbooks"/>
     <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
@@ -22638,8 +22281,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L115:L122 R115:R122 X115:X122 R103:R113 L103:L113 F103:F113 F115:F122 L91:L101 R91:R101 X91:X101 X103:X113 R79:R89 L79:L89 F79:F89 F91:F101 L67:L77 R67:R77 X67:X77 X79:X89 R55:R65 L55:L65 F55:F65 F67:F77 L43:L53 R43:R53 X43:X53 X55:X65 R31:R41 L31:L41 F31:F41 F43:F53 L21:L29 R21:R29 X21:X29 X31:X41 R12:R19 L12:L19 F12:F19 F21:F29 F3:F10 L3:L10 R3:R10 X3:X10 X12:X19" xr:uid="{9E153ADD-6094-4EEE-9D85-4BA3630B5D81}">
+      <formula1>"2024,2025  ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
